--- a/network_folder_simplified/sent_noti_now.xlsx
+++ b/network_folder_simplified/sent_noti_now.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notifications_Now" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notifications" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -125,16 +137,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NotificationsNow" displayName="NotificationsNow" ref="A1:E1" headerRowCount="1">
-  <autoFilter ref="A1:E1"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NotificationQueue" displayName="NotificationQueue" ref="A1:F29" headerRowCount="1">
+  <autoFilter ref="A1:F29"/>
+  <tableColumns count="6">
     <tableColumn id="1" name="EmployeeID"/>
     <tableColumn id="2" name="ContactEmail"/>
     <tableColumn id="3" name="Message"/>
     <tableColumn id="4" name="NotificationType"/>
     <tableColumn id="5" name="Priority"/>
+    <tableColumn id="6" name="NTStatusSent"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -427,41 +440,879 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>EmployeeID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ContactEmail</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Message</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>NotificationType</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>NTStatusSent</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP005</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>david.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Weekly vendor timesheet report ready</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Manager Summary</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>test001@company.com</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Please review team submissions</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Manager Summary</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>john.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Timesheet hours mismatch detected</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mismatch Alert</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>EMP002</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>jane.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Discrepancy found in logged hours</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mismatch Alert</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mike.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Please review and correct timesheet entries</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mismatch Alert</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>sarah.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Timesheet hours mismatch detected</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mismatch Alert</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EMP005</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>david.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Discrepancy found in logged hours</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Mismatch Alert</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>test001@company.com</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Please review and correct timesheet entries</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mismatch Alert</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP001</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>john.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>General notification</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>System Alert</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP002</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>jane.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>General notification</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>System Alert</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>mike.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>General notification</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>System Alert</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>sarah.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>General notification</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>System Alert</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP005</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>david.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>General notification</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>System Alert</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>test001@company.com</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>General notification</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>System Alert</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP001</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>john.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>General notification</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Holiday Reminder</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP002</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>jane.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>General notification</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Holiday Reminder</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>mike.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>General notification</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Holiday Reminder</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>sarah.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>General notification</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Holiday Reminder</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP005</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>david.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>General notification</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Holiday Reminder</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>test001@company.com</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>General notification</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Holiday Reminder</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP001</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>john.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Timesheet submission is overdue</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Late Submission</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP002</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>jane.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Urgent: Submit pending timesheet</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Late Submission</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP003</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>mike.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Final reminder for timesheet submission</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Late Submission</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP004</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>sarah.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Timesheet submission is overdue</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Late Submission</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>EMP005</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>david.vendor@company.com</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Urgent: Submit pending timesheet</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Late Submission</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>test001@company.com</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Final reminder for timesheet submission</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Late Submission</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>test@example.com</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Test notification added at 04:35:35</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Test Sync</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SYNC_TEST</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>sync@test.com</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Sync test at 2025-09-12 04:36:22</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sync Test</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
